--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104737_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104737_W31.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5169</v>
+        <v>6.3161</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0675</v>
+        <v>4.6276</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4493</v>
+        <v>1.6885</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0562</v>
+        <v>3.0491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3952</v>
+        <v>0.3937</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6609</v>
+        <v>2.6554</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2634</v>
+        <v>2.2427</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9513</v>
+        <v>0.9405</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3121</v>
+        <v>1.3022</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7927</v>
+        <v>0.8063</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5561</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3488</v>
+        <v>1.3532</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1319</v>
+        <v>-0.317</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3474</v>
+        <v>-0.0609</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4793</v>
+        <v>-0.256</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5926</v>
+        <v>3.584</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5926</v>
+        <v>3.584</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6925</v>
+        <v>3.3951</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5919</v>
+        <v>1.3977</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1006</v>
+        <v>1.9974</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0037</v>
+        <v>4.0009</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5238</v>
+        <v>2.5217</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4799</v>
+        <v>1.4792</v>
       </c>
       <c r="J3" t="n">
-        <v>2.796</v>
+        <v>2.7801</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4104</v>
+        <v>3.3989</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6145</v>
+        <v>-0.6188</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2078</v>
+        <v>1.2208</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8867</v>
+        <v>-0.8772</v>
       </c>
       <c r="O3" t="n">
-        <v>2.0944</v>
+        <v>2.098</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2665</v>
+        <v>-0.5571</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1828</v>
+        <v>-0.3534</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0837</v>
+        <v>-0.2037</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9472</v>
+        <v>2.8007</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8037</v>
+        <v>-0.348</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1434</v>
+        <v>3.1487</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4575</v>
+        <v>1.3035</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8663</v>
+        <v>-0.2758</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5911999999999999</v>
+        <v>1.5793</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5495</v>
+        <v>-0.2036</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4749</v>
+        <v>-0.2036</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.092</v>
+        <v>1.5071</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6086</v>
+        <v>-0.0722</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5165999999999999</v>
+        <v>1.5793</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2272</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5575</v>
+        <v>0.4972</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2308</v>
+        <v>-0.3022</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3267</v>
+        <v>0.7994</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1594</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9348</v>
+        <v>2.5322</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5782</v>
+        <v>1.141</v>
       </c>
       <c r="F5" t="n">
-        <v>3.513</v>
+        <v>1.3912</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3013</v>
+        <v>2.9676</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2765</v>
+        <v>1.7926</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5778</v>
+        <v>1.1749</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2013</v>
+        <v>2.2623</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2013</v>
+        <v>3.3882</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.1259</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5026</v>
+        <v>0.7053</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0752</v>
+        <v>-1.5956</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5778</v>
+        <v>2.3008</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4544</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4544</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6335</v>
+        <v>-0.4354</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5363</v>
+        <v>-0.5279</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1697</v>
+        <v>0.0925</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5456</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1594</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3862</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4237</v>
+        <v>1.9943</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2782</v>
+        <v>0.9641</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1455</v>
+        <v>1.0302</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9756</v>
+        <v>1.4578</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7973</v>
+        <v>0.8646</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1783</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2881</v>
+        <v>1.5429</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4052</v>
+        <v>1.4684</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1171</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6875</v>
+        <v>-0.0851</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.608</v>
+        <v>-0.6037</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2955</v>
+        <v>0.5187</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1359</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5519</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4196</v>
+        <v>0.4016</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1323</v>
+        <v>0.2047</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5456</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0316</v>
+        <v>0.0586</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5098</v>
+        <v>-1.3949</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5414</v>
+        <v>1.4536</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8462</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1045</v>
+        <v>-1.1055</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2583</v>
+        <v>0.2593</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2322</v>
+        <v>-1.2345</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2322</v>
+        <v>-1.2345</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.386</v>
+        <v>0.3884</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1277</v>
+        <v>0.129</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2583</v>
+        <v>0.2593</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1962</v>
+        <v>0.2219</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2776</v>
+        <v>-0.1604</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4738</v>
+        <v>0.3823</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1294</v>
+        <v>-0.359</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7184</v>
+        <v>-0.3351</v>
       </c>
       <c r="F8" t="n">
-        <v>2.589</v>
+        <v>-0.0239</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3304</v>
+        <v>0.6876</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2398</v>
+        <v>-0.3974</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9094</v>
+        <v>1.0849</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.756</v>
+        <v>0.1694</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8866000000000001</v>
+        <v>0.8101</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.6407</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4257</v>
+        <v>0.5181</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3532</v>
+        <v>-1.2075</v>
       </c>
       <c r="O8" t="n">
-        <v>1.7789</v>
+        <v>1.7256</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4544</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1097</v>
+        <v>-0.0057</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.372</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4817</v>
+        <v>0.4988</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5456</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5456</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
@@ -1111,22 +1111,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4214</v>
+        <v>-0.3898</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0694</v>
+        <v>-0.0697</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.352</v>
+        <v>-0.3201</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2064</v>
+        <v>-0.1754</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0694</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.137</v>
+        <v>-0.1057</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4614</v>
+        <v>-0.4306</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5853</v>
+        <v>-2.6621</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1239</v>
+        <v>2.2315</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0165</v>
+        <v>-0.3251</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3073</v>
+        <v>-1.2355</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2909</v>
+        <v>0.9103</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1226</v>
+        <v>-1.7616</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.8898</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5159</v>
+        <v>-0.8718</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1062</v>
+        <v>1.4365</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6688</v>
+        <v>-0.3457</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7749</v>
+        <v>1.7821</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7262</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4078</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2582</v>
+        <v>-0.195</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6945</v>
+        <v>-0.3071</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4363</v>
+        <v>0.1121</v>
       </c>
       <c r="V10" t="n">
-        <v>2.0231</v>
+        <v>0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2507</v>
+        <v>0.5447</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3738</v>
+        <v>-1.1331</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9191</v>
+        <v>-2.3666</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4547</v>
+        <v>1.2335</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6768</v>
+        <v>-0.0151</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.405</v>
+        <v>-1.3067</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0818</v>
+        <v>1.2917</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1724</v>
+        <v>-0.1316</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8122</v>
+        <v>-0.6452</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6398</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5043</v>
+        <v>0.1165</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2173</v>
+        <v>-0.6615</v>
       </c>
       <c r="O11" t="n">
-        <v>1.7216</v>
+        <v>0.778</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1359</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1359</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0041</v>
+        <v>-0.4076</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0915</v>
+        <v>-0.0678</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.3399</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1825</v>
+        <v>2.0212</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1825</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8991</v>
+        <v>-1.715</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0062</v>
+        <v>-0.7725</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8929</v>
+        <v>-0.9425</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1983</v>
+        <v>-0.1949</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3734</v>
+        <v>-0.3708</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1751</v>
+        <v>0.1759</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.6979</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4987</v>
+        <v>0.503</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3907</v>
+        <v>-0.3881</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8894</v>
+        <v>0.8911</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0278</v>
+        <v>0.202</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3091</v>
+        <v>-0.0746</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3369</v>
+        <v>0.2766</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9557</v>
+        <v>-1.9497</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.9557</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9735</v>
+        <v>-2.4274</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0607</v>
+        <v>-3.7176</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0872</v>
+        <v>1.2902</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2619</v>
+        <v>-1.2568</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1015</v>
+        <v>-1.0976</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1604</v>
+        <v>-0.1592</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2526</v>
+        <v>-1.2575</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2134</v>
+        <v>0.2101</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.466</v>
+        <v>-1.4676</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0094</v>
+        <v>0.0007</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3149</v>
+        <v>-1.3077</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3055</v>
+        <v>1.3083</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3484</v>
+        <v>0.1952</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5363</v>
+        <v>-0.1838</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1879</v>
+        <v>0.379</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.2881</v>
+        <v>10.6421</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.7058</v>
+        <v>-3.536100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>13.9937</v>
+        <v>14.1783</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6028</v>
+        <v>10.614</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2254</v>
+        <v>-0.2167000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>10.8282</v>
+        <v>10.8305</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8076</v>
+        <v>3.710700000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.325999999999999</v>
+        <v>7.260299999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.5186</v>
+        <v>-3.5497</v>
       </c>
       <c r="M14" t="n">
-        <v>6.7951</v>
+        <v>6.9032</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.5518</v>
+        <v>-7.4771</v>
       </c>
       <c r="O14" t="n">
-        <v>14.3467</v>
+        <v>14.38</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.4077</v>
+        <v>-3.414499999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4952</v>
+        <v>-12.5199</v>
       </c>
       <c r="R14" t="n">
-        <v>9.087399999999999</v>
+        <v>9.105400000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7263000000000004</v>
+        <v>-0.3705000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.5219</v>
+        <v>-2.210700000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7956</v>
+        <v>1.8401</v>
       </c>
       <c r="V14" t="n">
-        <v>3.819399999999999</v>
+        <v>3.8133</v>
       </c>
       <c r="W14" t="n">
-        <v>7.504</v>
+        <v>7.4834</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.6846</v>
+        <v>-3.6702</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7762</v>
+        <v>2.1948</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2742</v>
+        <v>2.2481</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.498</v>
+        <v>-0.0533</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9124</v>
+        <v>1.4702</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3585</v>
+        <v>0.5805</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.8897</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9676</v>
+        <v>2.7037</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9303</v>
+        <v>2.592</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.1117</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9449</v>
+        <v>-1.2335</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4282</v>
+        <v>-2.0116</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.778</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2272</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6816</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7513</v>
+        <v>0.2693</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5338</v>
+        <v>-0.407</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2175</v>
+        <v>0.6763</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.3419</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3419</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5655</v>
+        <v>1.5949</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8611</v>
+        <v>2.0774</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2956</v>
+        <v>-0.4825</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4698</v>
+        <v>2.9062</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5831</v>
+        <v>2.3503</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8868</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7161</v>
+        <v>1.957</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6043</v>
+        <v>1.9198</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1118</v>
+        <v>0.0372</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2463</v>
+        <v>0.9492</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0212</v>
+        <v>0.4305</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7749</v>
+        <v>0.5187</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1359</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5903</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6413</v>
+        <v>0.5702</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1897</v>
+        <v>0.348</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4516</v>
+        <v>0.2221</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0913</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0111</v>
+        <v>0.7467</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5821</v>
+        <v>-0.0038</v>
       </c>
       <c r="F17" t="n">
-        <v>0.571</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.7947</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3089</v>
+        <v>-1.3044</v>
       </c>
       <c r="I17" t="n">
-        <v>0.508</v>
+        <v>0.5097</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4847</v>
+        <v>0.4797</v>
       </c>
       <c r="K17" t="n">
-        <v>0.006</v>
+        <v>0.0033</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4787</v>
+        <v>0.4764</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2856</v>
+        <v>-1.2744</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3149</v>
+        <v>-1.3077</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0293</v>
+        <v>0.0333</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3692</v>
+        <v>0.382</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0221</v>
+        <v>-0.4348</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6529</v>
+        <v>0.8168</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9318</v>
+        <v>0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2515</v>
+        <v>0.6176</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0954</v>
+        <v>-1.7136</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1561</v>
+        <v>2.3312</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8833</v>
+        <v>0.9482</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.695</v>
+        <v>0.8259</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1883</v>
+        <v>0.1222</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4399</v>
+        <v>1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7776999999999999</v>
+        <v>2.3637</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.2176</v>
+        <v>-0.8138</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4434</v>
+        <v>-0.6018</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4727</v>
+        <v>-1.5378</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0293</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3631</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2687</v>
+        <v>0.0172</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3446</v>
+        <v>-0.6395</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0759</v>
+        <v>0.6567</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.018</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.018</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4541</v>
+        <v>-0.7577</v>
       </c>
       <c r="E19" t="n">
-        <v>0.876</v>
+        <v>-0.4742</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3301</v>
+        <v>-0.2835</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0896</v>
+        <v>-1.1757</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6401</v>
+        <v>-0.6261</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5506</v>
+        <v>-0.5496</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1816</v>
+        <v>-0.7179</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9332</v>
+        <v>-0.7552</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7516</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.092</v>
+        <v>-0.4578</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2931</v>
+        <v>0.129</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2011</v>
+        <v>-0.5868</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9087</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9087</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0489</v>
+        <v>0.1903</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6945</v>
+        <v>0.2437</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3545</v>
+        <v>-0.0534</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.5013</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4665</v>
+        <v>-0.798</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1174</v>
+        <v>-1.2869</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3491</v>
+        <v>0.4889</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1772</v>
+        <v>-2.8766</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6266</v>
+        <v>-0.6899</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5506</v>
+        <v>-2.1867</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7171</v>
+        <v>-1.4443</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7543</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>-2.22</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4601</v>
+        <v>-1.4323</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1277</v>
+        <v>-1.4656</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5878</v>
+        <v>0.0333</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2272</v>
+        <v>1.3658</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2272</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4835</v>
+        <v>0.7129</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5996</v>
+        <v>0.1574</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1161</v>
+        <v>0.5554</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6025</v>
+        <v>-0.9789</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7215</v>
+        <v>-2.1672</v>
       </c>
       <c r="F21" t="n">
-        <v>2.119</v>
+        <v>1.1883</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9717</v>
+        <v>-2.2172</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8386</v>
+        <v>0.0978</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1331</v>
+        <v>-2.315</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5869</v>
+        <v>-2.6942</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3865</v>
+        <v>-0.1314</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7996</v>
+        <v>-2.5628</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6151</v>
+        <v>0.477</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5479</v>
+        <v>0.2292</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9327</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3631</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.635</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2719</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.235</v>
+        <v>-0.1487</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.6972</v>
+        <v>-0.3349</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4623</v>
+        <v>0.1862</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0238</v>
+        <v>0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0238</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9704</v>
+        <v>-1.1029</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8623</v>
+        <v>0.3963</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8919</v>
+        <v>-1.4991</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2156</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0992</v>
+        <v>0.6429</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3148</v>
+        <v>-0.5496</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6853</v>
+        <v>0.1784</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1262</v>
+        <v>0.9308</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.5591</v>
+        <v>-0.7524</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4697</v>
+        <v>-0.0851</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2254</v>
+        <v>-0.2879</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2443</v>
+        <v>0.2028</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4544</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.141</v>
+        <v>0.3878</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0411</v>
+        <v>0.2179</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0999</v>
+        <v>0.1699</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9318</v>
+        <v>-2.4945</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1594</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0992</v>
+        <v>-1.7376</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4443</v>
+        <v>-3.2218</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3451</v>
+        <v>1.4842</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6244</v>
+        <v>-2.6247</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1923</v>
+        <v>0.1924</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8167</v>
+        <v>-2.8171</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9334</v>
+        <v>-2.9425</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1849</v>
+        <v>0.1789</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.1183</v>
+        <v>-3.1213</v>
       </c>
       <c r="M23" t="n">
-        <v>0.309</v>
+        <v>0.3178</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0075</v>
+        <v>0.0135</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3016</v>
+        <v>0.3043</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3836</v>
+        <v>-0.0234</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2837</v>
+        <v>-0.0517</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0999</v>
+        <v>0.0283</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2608</v>
+        <v>-3.6558</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7818</v>
+        <v>-2.8566</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.479</v>
+        <v>-0.7991</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9505</v>
+        <v>-2.9501</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5898</v>
+        <v>-0.5888</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3607</v>
+        <v>-2.3613</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3465</v>
+        <v>-1.3586</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1008</v>
+        <v>1.0924</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.4473</v>
+        <v>-2.4511</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.604</v>
+        <v>-1.5915</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6906</v>
+        <v>-1.6813</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0866</v>
+        <v>0.0898</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1282</v>
+        <v>0.4749</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0726</v>
+        <v>-0.1306</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9444</v>
+        <v>0.6055</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8637</v>
+        <v>-1.8634</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2292</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5136</v>
+        <v>-4.8375</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.014</v>
+        <v>-6.7889</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5004</v>
+        <v>1.9514</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.3944</v>
+        <v>-3.3927</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.266</v>
+        <v>-1.2639</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.1284</v>
+        <v>-2.1289</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.6097</v>
+        <v>-4.6144</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.4914</v>
+        <v>-1.4931</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.1183</v>
+        <v>-3.1213</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2153</v>
+        <v>1.2217</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2254</v>
+        <v>0.2292</v>
       </c>
       <c r="O25" t="n">
-        <v>0.99</v>
+        <v>0.9925</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2104</v>
+        <v>-0.5342</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0411</v>
+        <v>-0.8087</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1693</v>
+        <v>0.2744</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.288</v>
+        <v>-8.714400000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-13.6075</v>
+        <v>-13.7912</v>
       </c>
       <c r="F26" t="n">
-        <v>3.3195</v>
+        <v>5.076999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-10.6028</v>
+        <v>-10.6138</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2254999999999998</v>
+        <v>0.2166999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-10.8283</v>
+        <v>-10.8307</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.795</v>
+        <v>-6.903099999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>7.551799999999998</v>
+        <v>7.476899999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-14.3467</v>
+        <v>-14.3802</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.8076</v>
+        <v>-3.710699999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.326199999999999</v>
+        <v>-7.260500000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5186</v>
+        <v>3.5496</v>
       </c>
       <c r="P26" t="n">
-        <v>3.4079</v>
+        <v>3.4145</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.087399999999999</v>
+        <v>-9.1053</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4953</v>
+        <v>12.5198</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7262999999999993</v>
+        <v>2.2983</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.795599999999999</v>
+        <v>-1.8402</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5221</v>
+        <v>4.1382</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.8195</v>
+        <v>-3.8132</v>
       </c>
       <c r="W26" t="n">
-        <v>4.0709</v>
+        <v>4.057300000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.8902</v>
+        <v>-7.8705</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104737_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104737_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.6702</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104737_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.8705</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
